--- a/public/성과분석조사_프레임.xlsx
+++ b/public/성과분석조사_프레임.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\공유폴더\★ 2026년 부산시 펀드현황 및 성과분석 용역\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A01451-3A24-4DD8-ABF2-600F1FDD1068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15BEA0E-887C-40FA-8E47-8F7D45C4ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="29040" windowHeight="15720" xr2:uid="{B7AAC534-F7B5-4439-A0A3-F4DB4056948B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7AAC534-F7B5-4439-A0A3-F4DB4056948B}"/>
   </bookViews>
   <sheets>
     <sheet name="펀드 조합현황" sheetId="2" r:id="rId1"/>
@@ -766,7 +766,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="183">
   <si>
     <t>DQ01. 운용사명</t>
   </si>
@@ -1628,6 +1628,40 @@
   <si>
     <t>1-1. 운용사 정보</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>투자후 +4년</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>투자후 +6년</t>
+  </si>
+  <si>
+    <t>투자후 +7년</t>
+  </si>
+  <si>
+    <t>투자후 +8년</t>
+  </si>
+  <si>
+    <t>투자후 +9년</t>
+  </si>
+  <si>
+    <t>투자후 +10년</t>
+  </si>
+  <si>
+    <t>투자후 +11년</t>
+  </si>
+  <si>
+    <t>투자후 +12년</t>
+  </si>
+  <si>
+    <t>투자후 +13년</t>
+  </si>
+  <si>
+    <t>투자후 +14년</t>
+  </si>
+  <si>
+    <t>투자후 +15년</t>
   </si>
 </sst>
 </file>
@@ -3195,11 +3229,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="CA1:CC2"/>
-    <mergeCell ref="CD1:CI1"/>
-    <mergeCell ref="CD2:CE2"/>
-    <mergeCell ref="CF2:CG2"/>
-    <mergeCell ref="CH2:CI2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="BM2:BZ2"/>
     <mergeCell ref="AK1:BZ1"/>
@@ -3208,6 +3237,11 @@
     <mergeCell ref="AY2:BL2"/>
     <mergeCell ref="M1:W2"/>
     <mergeCell ref="B1:L2"/>
+    <mergeCell ref="CA1:CC2"/>
+    <mergeCell ref="CD1:CI1"/>
+    <mergeCell ref="CD2:CE2"/>
+    <mergeCell ref="CF2:CG2"/>
+    <mergeCell ref="CH2:CI2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3220,7 +3254,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BT27"/>
+  <dimension ref="A1:CN27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="10.625" customWidth="1"/>
@@ -3252,13 +3286,22 @@
     <col min="50" max="50" width="20.375" customWidth="1"/>
     <col min="51" max="51" width="15" customWidth="1"/>
     <col min="52" max="52" width="16.75" customWidth="1"/>
-    <col min="53" max="55" width="10.625" customWidth="1"/>
-    <col min="56" max="56" width="15.375" customWidth="1"/>
-    <col min="57" max="72" width="10.625" customWidth="1"/>
+    <col min="53" max="59" width="10.625" customWidth="1"/>
+    <col min="60" max="60" width="11.75" customWidth="1"/>
+    <col min="61" max="65" width="11.125" customWidth="1"/>
+    <col min="66" max="66" width="15.375" customWidth="1"/>
+    <col min="67" max="77" width="10.625" customWidth="1"/>
+    <col min="78" max="78" width="11.125" customWidth="1"/>
+    <col min="79" max="79" width="11.5" customWidth="1"/>
+    <col min="80" max="80" width="12" customWidth="1"/>
+    <col min="81" max="81" width="11.75" customWidth="1"/>
+    <col min="82" max="82" width="11.5" customWidth="1"/>
+    <col min="83" max="83" width="11.25" customWidth="1"/>
+    <col min="84" max="92" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:72" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:92" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:92" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="69" t="s">
         <v>66</v>
       </c>
@@ -3279,7 +3322,7 @@
       <c r="P2" s="70"/>
       <c r="Q2" s="71"/>
     </row>
-    <row r="3" spans="1:72" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:92" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="72"/>
       <c r="B3" s="73"/>
       <c r="C3" s="73"/>
@@ -3298,7 +3341,7 @@
       <c r="P3" s="73"/>
       <c r="Q3" s="74"/>
     </row>
-    <row r="4" spans="1:72" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:92" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>67</v>
       </c>
@@ -3317,7 +3360,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:72" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:92" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
         <v>68</v>
       </c>
@@ -3394,8 +3437,28 @@
       <c r="BR5" s="78"/>
       <c r="BS5" s="78"/>
       <c r="BT5" s="78"/>
+      <c r="BU5" s="78"/>
+      <c r="BV5" s="78"/>
+      <c r="BW5" s="78"/>
+      <c r="BX5" s="78"/>
+      <c r="BY5" s="78"/>
+      <c r="BZ5" s="78"/>
+      <c r="CA5" s="78"/>
+      <c r="CB5" s="78"/>
+      <c r="CC5" s="78"/>
+      <c r="CD5" s="78"/>
+      <c r="CE5" s="78"/>
+      <c r="CF5" s="78"/>
+      <c r="CG5" s="78"/>
+      <c r="CH5" s="78"/>
+      <c r="CI5" s="78"/>
+      <c r="CJ5" s="78"/>
+      <c r="CK5" s="78"/>
+      <c r="CL5" s="78"/>
+      <c r="CM5" s="78"/>
+      <c r="CN5" s="78"/>
     </row>
-    <row r="6" spans="1:72" s="62" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:92" s="62" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79" t="s">
         <v>70</v>
       </c>
@@ -3550,28 +3613,48 @@
       <c r="BB6" s="82"/>
       <c r="BC6" s="82"/>
       <c r="BD6" s="82"/>
-      <c r="BE6" s="83" t="s">
+      <c r="BE6" s="82"/>
+      <c r="BF6" s="82"/>
+      <c r="BG6" s="82"/>
+      <c r="BH6" s="82"/>
+      <c r="BI6" s="82"/>
+      <c r="BJ6" s="82"/>
+      <c r="BK6" s="82"/>
+      <c r="BL6" s="82"/>
+      <c r="BM6" s="82"/>
+      <c r="BN6" s="82"/>
+      <c r="BO6" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="BF6" s="83"/>
-      <c r="BG6" s="83"/>
-      <c r="BH6" s="83"/>
-      <c r="BI6" s="83"/>
-      <c r="BJ6" s="83"/>
-      <c r="BK6" s="83"/>
-      <c r="BL6" s="83"/>
-      <c r="BM6" s="68" t="s">
+      <c r="BP6" s="83"/>
+      <c r="BQ6" s="83"/>
+      <c r="BR6" s="83"/>
+      <c r="BS6" s="83"/>
+      <c r="BT6" s="83"/>
+      <c r="BU6" s="83"/>
+      <c r="BV6" s="83"/>
+      <c r="BW6" s="83"/>
+      <c r="BX6" s="83"/>
+      <c r="BY6" s="83"/>
+      <c r="BZ6" s="83"/>
+      <c r="CA6" s="83"/>
+      <c r="CB6" s="83"/>
+      <c r="CC6" s="83"/>
+      <c r="CD6" s="83"/>
+      <c r="CE6" s="83"/>
+      <c r="CF6" s="83"/>
+      <c r="CG6" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="BN6" s="68"/>
-      <c r="BO6" s="68"/>
-      <c r="BP6" s="68"/>
-      <c r="BQ6" s="68"/>
-      <c r="BR6" s="68"/>
-      <c r="BS6" s="68"/>
-      <c r="BT6" s="68"/>
+      <c r="CH6" s="68"/>
+      <c r="CI6" s="68"/>
+      <c r="CJ6" s="68"/>
+      <c r="CK6" s="68"/>
+      <c r="CL6" s="68"/>
+      <c r="CM6" s="68"/>
+      <c r="CN6" s="68"/>
     </row>
-    <row r="7" spans="1:72" s="63" customFormat="1" ht="81" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:92" s="63" customFormat="1" ht="81" x14ac:dyDescent="0.3">
       <c r="A7" s="80"/>
       <c r="B7" s="80"/>
       <c r="C7" s="80"/>
@@ -3718,64 +3801,124 @@
         <v>162</v>
       </c>
       <c r="BB7" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="BC7" s="16" t="s">
         <v>164</v>
       </c>
       <c r="BD7" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="BE7" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="BF7" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="BG7" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="BH7" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI7" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="BJ7" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="BK7" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="BL7" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="BM7" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="BN7" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="BE7" s="15" t="s">
+      <c r="BO7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="BF7" s="15" t="s">
+      <c r="BP7" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="BG7" s="15" t="s">
+      <c r="BQ7" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="BH7" s="15" t="s">
+      <c r="BR7" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="BI7" s="15" t="s">
+      <c r="BS7" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="BJ7" s="15" t="s">
+      <c r="BT7" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="BK7" s="15" t="s">
+      <c r="BU7" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BL7" s="15" t="s">
+      <c r="BV7" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="BW7" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="BX7" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="BY7" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="BZ7" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="CA7" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="CB7" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="CC7" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="CD7" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="CE7" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="CF7" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="BM7" s="18" t="s">
+      <c r="CG7" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="BN7" s="18" t="s">
+      <c r="CH7" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="BO7" s="18" t="s">
+      <c r="CI7" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="BP7" s="18" t="s">
+      <c r="CJ7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="BQ7" s="18" t="s">
+      <c r="CK7" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="BR7" s="18" t="s">
+      <c r="CL7" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="BS7" s="18" t="s">
+      <c r="CM7" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="BT7" s="18" t="s">
+      <c r="CN7" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>1</v>
       </c>
@@ -3833,7 +3976,7 @@
       <c r="BA8" s="33"/>
       <c r="BB8" s="33"/>
       <c r="BC8" s="33"/>
-      <c r="BD8" s="34"/>
+      <c r="BD8" s="33"/>
       <c r="BE8" s="33"/>
       <c r="BF8" s="33"/>
       <c r="BG8" s="33"/>
@@ -3841,17 +3984,37 @@
       <c r="BI8" s="33"/>
       <c r="BJ8" s="33"/>
       <c r="BK8" s="33"/>
-      <c r="BL8" s="34"/>
+      <c r="BL8" s="33"/>
       <c r="BM8" s="33"/>
-      <c r="BN8" s="33"/>
+      <c r="BN8" s="34"/>
       <c r="BO8" s="33"/>
       <c r="BP8" s="33"/>
       <c r="BQ8" s="33"/>
       <c r="BR8" s="33"/>
       <c r="BS8" s="33"/>
-      <c r="BT8" s="35"/>
+      <c r="BT8" s="33"/>
+      <c r="BU8" s="33"/>
+      <c r="BV8" s="33"/>
+      <c r="BW8" s="33"/>
+      <c r="BX8" s="33"/>
+      <c r="BY8" s="33"/>
+      <c r="BZ8" s="33"/>
+      <c r="CA8" s="33"/>
+      <c r="CB8" s="33"/>
+      <c r="CC8" s="33"/>
+      <c r="CD8" s="33"/>
+      <c r="CE8" s="33"/>
+      <c r="CF8" s="34"/>
+      <c r="CG8" s="33"/>
+      <c r="CH8" s="33"/>
+      <c r="CI8" s="33"/>
+      <c r="CJ8" s="33"/>
+      <c r="CK8" s="33"/>
+      <c r="CL8" s="33"/>
+      <c r="CM8" s="33"/>
+      <c r="CN8" s="35"/>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A9" s="20"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3907,7 +4070,7 @@
       <c r="BA9" s="33"/>
       <c r="BB9" s="33"/>
       <c r="BC9" s="33"/>
-      <c r="BD9" s="34"/>
+      <c r="BD9" s="33"/>
       <c r="BE9" s="33"/>
       <c r="BF9" s="33"/>
       <c r="BG9" s="33"/>
@@ -3915,17 +4078,37 @@
       <c r="BI9" s="33"/>
       <c r="BJ9" s="33"/>
       <c r="BK9" s="33"/>
-      <c r="BL9" s="34"/>
+      <c r="BL9" s="33"/>
       <c r="BM9" s="33"/>
-      <c r="BN9" s="33"/>
+      <c r="BN9" s="34"/>
       <c r="BO9" s="33"/>
       <c r="BP9" s="33"/>
       <c r="BQ9" s="33"/>
       <c r="BR9" s="33"/>
       <c r="BS9" s="33"/>
-      <c r="BT9" s="35"/>
+      <c r="BT9" s="33"/>
+      <c r="BU9" s="33"/>
+      <c r="BV9" s="33"/>
+      <c r="BW9" s="33"/>
+      <c r="BX9" s="33"/>
+      <c r="BY9" s="33"/>
+      <c r="BZ9" s="33"/>
+      <c r="CA9" s="33"/>
+      <c r="CB9" s="33"/>
+      <c r="CC9" s="33"/>
+      <c r="CD9" s="33"/>
+      <c r="CE9" s="33"/>
+      <c r="CF9" s="34"/>
+      <c r="CG9" s="33"/>
+      <c r="CH9" s="33"/>
+      <c r="CI9" s="33"/>
+      <c r="CJ9" s="33"/>
+      <c r="CK9" s="33"/>
+      <c r="CL9" s="33"/>
+      <c r="CM9" s="33"/>
+      <c r="CN9" s="35"/>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -3981,7 +4164,7 @@
       <c r="BA10" s="33"/>
       <c r="BB10" s="33"/>
       <c r="BC10" s="33"/>
-      <c r="BD10" s="34"/>
+      <c r="BD10" s="33"/>
       <c r="BE10" s="33"/>
       <c r="BF10" s="33"/>
       <c r="BG10" s="33"/>
@@ -3989,17 +4172,37 @@
       <c r="BI10" s="33"/>
       <c r="BJ10" s="33"/>
       <c r="BK10" s="33"/>
-      <c r="BL10" s="34"/>
+      <c r="BL10" s="33"/>
       <c r="BM10" s="33"/>
-      <c r="BN10" s="33"/>
+      <c r="BN10" s="34"/>
       <c r="BO10" s="33"/>
       <c r="BP10" s="33"/>
       <c r="BQ10" s="33"/>
       <c r="BR10" s="33"/>
       <c r="BS10" s="33"/>
-      <c r="BT10" s="35"/>
+      <c r="BT10" s="33"/>
+      <c r="BU10" s="33"/>
+      <c r="BV10" s="33"/>
+      <c r="BW10" s="33"/>
+      <c r="BX10" s="33"/>
+      <c r="BY10" s="33"/>
+      <c r="BZ10" s="33"/>
+      <c r="CA10" s="33"/>
+      <c r="CB10" s="33"/>
+      <c r="CC10" s="33"/>
+      <c r="CD10" s="33"/>
+      <c r="CE10" s="33"/>
+      <c r="CF10" s="34"/>
+      <c r="CG10" s="33"/>
+      <c r="CH10" s="33"/>
+      <c r="CI10" s="33"/>
+      <c r="CJ10" s="33"/>
+      <c r="CK10" s="33"/>
+      <c r="CL10" s="33"/>
+      <c r="CM10" s="33"/>
+      <c r="CN10" s="35"/>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -4055,7 +4258,7 @@
       <c r="BA11" s="33"/>
       <c r="BB11" s="33"/>
       <c r="BC11" s="33"/>
-      <c r="BD11" s="34"/>
+      <c r="BD11" s="33"/>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
@@ -4063,17 +4266,37 @@
       <c r="BI11" s="33"/>
       <c r="BJ11" s="33"/>
       <c r="BK11" s="33"/>
-      <c r="BL11" s="34"/>
+      <c r="BL11" s="33"/>
       <c r="BM11" s="33"/>
-      <c r="BN11" s="33"/>
+      <c r="BN11" s="34"/>
       <c r="BO11" s="33"/>
       <c r="BP11" s="33"/>
       <c r="BQ11" s="33"/>
       <c r="BR11" s="33"/>
       <c r="BS11" s="33"/>
-      <c r="BT11" s="35"/>
+      <c r="BT11" s="33"/>
+      <c r="BU11" s="33"/>
+      <c r="BV11" s="33"/>
+      <c r="BW11" s="33"/>
+      <c r="BX11" s="33"/>
+      <c r="BY11" s="33"/>
+      <c r="BZ11" s="33"/>
+      <c r="CA11" s="33"/>
+      <c r="CB11" s="33"/>
+      <c r="CC11" s="33"/>
+      <c r="CD11" s="33"/>
+      <c r="CE11" s="33"/>
+      <c r="CF11" s="34"/>
+      <c r="CG11" s="33"/>
+      <c r="CH11" s="33"/>
+      <c r="CI11" s="33"/>
+      <c r="CJ11" s="33"/>
+      <c r="CK11" s="33"/>
+      <c r="CL11" s="33"/>
+      <c r="CM11" s="33"/>
+      <c r="CN11" s="35"/>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A12" s="20"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -4129,7 +4352,7 @@
       <c r="BA12" s="33"/>
       <c r="BB12" s="33"/>
       <c r="BC12" s="33"/>
-      <c r="BD12" s="34"/>
+      <c r="BD12" s="33"/>
       <c r="BE12" s="33"/>
       <c r="BF12" s="33"/>
       <c r="BG12" s="33"/>
@@ -4137,17 +4360,37 @@
       <c r="BI12" s="33"/>
       <c r="BJ12" s="33"/>
       <c r="BK12" s="33"/>
-      <c r="BL12" s="34"/>
+      <c r="BL12" s="33"/>
       <c r="BM12" s="33"/>
-      <c r="BN12" s="33"/>
+      <c r="BN12" s="34"/>
       <c r="BO12" s="33"/>
       <c r="BP12" s="33"/>
       <c r="BQ12" s="33"/>
       <c r="BR12" s="33"/>
       <c r="BS12" s="33"/>
-      <c r="BT12" s="35"/>
+      <c r="BT12" s="33"/>
+      <c r="BU12" s="33"/>
+      <c r="BV12" s="33"/>
+      <c r="BW12" s="33"/>
+      <c r="BX12" s="33"/>
+      <c r="BY12" s="33"/>
+      <c r="BZ12" s="33"/>
+      <c r="CA12" s="33"/>
+      <c r="CB12" s="33"/>
+      <c r="CC12" s="33"/>
+      <c r="CD12" s="33"/>
+      <c r="CE12" s="33"/>
+      <c r="CF12" s="34"/>
+      <c r="CG12" s="33"/>
+      <c r="CH12" s="33"/>
+      <c r="CI12" s="33"/>
+      <c r="CJ12" s="33"/>
+      <c r="CK12" s="33"/>
+      <c r="CL12" s="33"/>
+      <c r="CM12" s="33"/>
+      <c r="CN12" s="35"/>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -4203,7 +4446,7 @@
       <c r="BA13" s="33"/>
       <c r="BB13" s="33"/>
       <c r="BC13" s="33"/>
-      <c r="BD13" s="34"/>
+      <c r="BD13" s="33"/>
       <c r="BE13" s="33"/>
       <c r="BF13" s="33"/>
       <c r="BG13" s="33"/>
@@ -4211,17 +4454,37 @@
       <c r="BI13" s="33"/>
       <c r="BJ13" s="33"/>
       <c r="BK13" s="33"/>
-      <c r="BL13" s="34"/>
+      <c r="BL13" s="33"/>
       <c r="BM13" s="33"/>
-      <c r="BN13" s="33"/>
+      <c r="BN13" s="34"/>
       <c r="BO13" s="33"/>
       <c r="BP13" s="33"/>
       <c r="BQ13" s="33"/>
       <c r="BR13" s="33"/>
       <c r="BS13" s="33"/>
-      <c r="BT13" s="35"/>
+      <c r="BT13" s="33"/>
+      <c r="BU13" s="33"/>
+      <c r="BV13" s="33"/>
+      <c r="BW13" s="33"/>
+      <c r="BX13" s="33"/>
+      <c r="BY13" s="33"/>
+      <c r="BZ13" s="33"/>
+      <c r="CA13" s="33"/>
+      <c r="CB13" s="33"/>
+      <c r="CC13" s="33"/>
+      <c r="CD13" s="33"/>
+      <c r="CE13" s="33"/>
+      <c r="CF13" s="34"/>
+      <c r="CG13" s="33"/>
+      <c r="CH13" s="33"/>
+      <c r="CI13" s="33"/>
+      <c r="CJ13" s="33"/>
+      <c r="CK13" s="33"/>
+      <c r="CL13" s="33"/>
+      <c r="CM13" s="33"/>
+      <c r="CN13" s="35"/>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -4277,7 +4540,7 @@
       <c r="BA14" s="33"/>
       <c r="BB14" s="33"/>
       <c r="BC14" s="33"/>
-      <c r="BD14" s="34"/>
+      <c r="BD14" s="33"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="33"/>
       <c r="BG14" s="33"/>
@@ -4285,17 +4548,37 @@
       <c r="BI14" s="33"/>
       <c r="BJ14" s="33"/>
       <c r="BK14" s="33"/>
-      <c r="BL14" s="34"/>
+      <c r="BL14" s="33"/>
       <c r="BM14" s="33"/>
-      <c r="BN14" s="33"/>
+      <c r="BN14" s="34"/>
       <c r="BO14" s="33"/>
       <c r="BP14" s="33"/>
       <c r="BQ14" s="33"/>
       <c r="BR14" s="33"/>
       <c r="BS14" s="33"/>
-      <c r="BT14" s="35"/>
+      <c r="BT14" s="33"/>
+      <c r="BU14" s="33"/>
+      <c r="BV14" s="33"/>
+      <c r="BW14" s="33"/>
+      <c r="BX14" s="33"/>
+      <c r="BY14" s="33"/>
+      <c r="BZ14" s="33"/>
+      <c r="CA14" s="33"/>
+      <c r="CB14" s="33"/>
+      <c r="CC14" s="33"/>
+      <c r="CD14" s="33"/>
+      <c r="CE14" s="33"/>
+      <c r="CF14" s="34"/>
+      <c r="CG14" s="33"/>
+      <c r="CH14" s="33"/>
+      <c r="CI14" s="33"/>
+      <c r="CJ14" s="33"/>
+      <c r="CK14" s="33"/>
+      <c r="CL14" s="33"/>
+      <c r="CM14" s="33"/>
+      <c r="CN14" s="35"/>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -4351,7 +4634,7 @@
       <c r="BA15" s="33"/>
       <c r="BB15" s="33"/>
       <c r="BC15" s="33"/>
-      <c r="BD15" s="34"/>
+      <c r="BD15" s="33"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="33"/>
       <c r="BG15" s="33"/>
@@ -4359,17 +4642,37 @@
       <c r="BI15" s="33"/>
       <c r="BJ15" s="33"/>
       <c r="BK15" s="33"/>
-      <c r="BL15" s="34"/>
+      <c r="BL15" s="33"/>
       <c r="BM15" s="33"/>
-      <c r="BN15" s="33"/>
+      <c r="BN15" s="34"/>
       <c r="BO15" s="33"/>
       <c r="BP15" s="33"/>
       <c r="BQ15" s="33"/>
       <c r="BR15" s="33"/>
       <c r="BS15" s="33"/>
-      <c r="BT15" s="35"/>
+      <c r="BT15" s="33"/>
+      <c r="BU15" s="33"/>
+      <c r="BV15" s="33"/>
+      <c r="BW15" s="33"/>
+      <c r="BX15" s="33"/>
+      <c r="BY15" s="33"/>
+      <c r="BZ15" s="33"/>
+      <c r="CA15" s="33"/>
+      <c r="CB15" s="33"/>
+      <c r="CC15" s="33"/>
+      <c r="CD15" s="33"/>
+      <c r="CE15" s="33"/>
+      <c r="CF15" s="34"/>
+      <c r="CG15" s="33"/>
+      <c r="CH15" s="33"/>
+      <c r="CI15" s="33"/>
+      <c r="CJ15" s="33"/>
+      <c r="CK15" s="33"/>
+      <c r="CL15" s="33"/>
+      <c r="CM15" s="33"/>
+      <c r="CN15" s="35"/>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -4425,7 +4728,7 @@
       <c r="BA16" s="33"/>
       <c r="BB16" s="33"/>
       <c r="BC16" s="33"/>
-      <c r="BD16" s="34"/>
+      <c r="BD16" s="33"/>
       <c r="BE16" s="33"/>
       <c r="BF16" s="33"/>
       <c r="BG16" s="33"/>
@@ -4433,17 +4736,37 @@
       <c r="BI16" s="33"/>
       <c r="BJ16" s="33"/>
       <c r="BK16" s="33"/>
-      <c r="BL16" s="34"/>
+      <c r="BL16" s="33"/>
       <c r="BM16" s="33"/>
-      <c r="BN16" s="33"/>
+      <c r="BN16" s="34"/>
       <c r="BO16" s="33"/>
       <c r="BP16" s="33"/>
       <c r="BQ16" s="33"/>
       <c r="BR16" s="33"/>
       <c r="BS16" s="33"/>
-      <c r="BT16" s="35"/>
+      <c r="BT16" s="33"/>
+      <c r="BU16" s="33"/>
+      <c r="BV16" s="33"/>
+      <c r="BW16" s="33"/>
+      <c r="BX16" s="33"/>
+      <c r="BY16" s="33"/>
+      <c r="BZ16" s="33"/>
+      <c r="CA16" s="33"/>
+      <c r="CB16" s="33"/>
+      <c r="CC16" s="33"/>
+      <c r="CD16" s="33"/>
+      <c r="CE16" s="33"/>
+      <c r="CF16" s="34"/>
+      <c r="CG16" s="33"/>
+      <c r="CH16" s="33"/>
+      <c r="CI16" s="33"/>
+      <c r="CJ16" s="33"/>
+      <c r="CK16" s="33"/>
+      <c r="CL16" s="33"/>
+      <c r="CM16" s="33"/>
+      <c r="CN16" s="35"/>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -4499,7 +4822,7 @@
       <c r="BA17" s="33"/>
       <c r="BB17" s="33"/>
       <c r="BC17" s="33"/>
-      <c r="BD17" s="34"/>
+      <c r="BD17" s="33"/>
       <c r="BE17" s="33"/>
       <c r="BF17" s="33"/>
       <c r="BG17" s="33"/>
@@ -4507,17 +4830,37 @@
       <c r="BI17" s="33"/>
       <c r="BJ17" s="33"/>
       <c r="BK17" s="33"/>
-      <c r="BL17" s="34"/>
+      <c r="BL17" s="33"/>
       <c r="BM17" s="33"/>
-      <c r="BN17" s="33"/>
+      <c r="BN17" s="34"/>
       <c r="BO17" s="33"/>
       <c r="BP17" s="33"/>
       <c r="BQ17" s="33"/>
       <c r="BR17" s="33"/>
       <c r="BS17" s="33"/>
-      <c r="BT17" s="35"/>
+      <c r="BT17" s="33"/>
+      <c r="BU17" s="33"/>
+      <c r="BV17" s="33"/>
+      <c r="BW17" s="33"/>
+      <c r="BX17" s="33"/>
+      <c r="BY17" s="33"/>
+      <c r="BZ17" s="33"/>
+      <c r="CA17" s="33"/>
+      <c r="CB17" s="33"/>
+      <c r="CC17" s="33"/>
+      <c r="CD17" s="33"/>
+      <c r="CE17" s="33"/>
+      <c r="CF17" s="34"/>
+      <c r="CG17" s="33"/>
+      <c r="CH17" s="33"/>
+      <c r="CI17" s="33"/>
+      <c r="CJ17" s="33"/>
+      <c r="CK17" s="33"/>
+      <c r="CL17" s="33"/>
+      <c r="CM17" s="33"/>
+      <c r="CN17" s="35"/>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -4573,7 +4916,7 @@
       <c r="BA18" s="33"/>
       <c r="BB18" s="33"/>
       <c r="BC18" s="33"/>
-      <c r="BD18" s="34"/>
+      <c r="BD18" s="33"/>
       <c r="BE18" s="33"/>
       <c r="BF18" s="33"/>
       <c r="BG18" s="33"/>
@@ -4581,17 +4924,37 @@
       <c r="BI18" s="33"/>
       <c r="BJ18" s="33"/>
       <c r="BK18" s="33"/>
-      <c r="BL18" s="34"/>
+      <c r="BL18" s="33"/>
       <c r="BM18" s="33"/>
-      <c r="BN18" s="33"/>
+      <c r="BN18" s="34"/>
       <c r="BO18" s="33"/>
       <c r="BP18" s="33"/>
       <c r="BQ18" s="33"/>
       <c r="BR18" s="33"/>
       <c r="BS18" s="33"/>
-      <c r="BT18" s="35"/>
+      <c r="BT18" s="33"/>
+      <c r="BU18" s="33"/>
+      <c r="BV18" s="33"/>
+      <c r="BW18" s="33"/>
+      <c r="BX18" s="33"/>
+      <c r="BY18" s="33"/>
+      <c r="BZ18" s="33"/>
+      <c r="CA18" s="33"/>
+      <c r="CB18" s="33"/>
+      <c r="CC18" s="33"/>
+      <c r="CD18" s="33"/>
+      <c r="CE18" s="33"/>
+      <c r="CF18" s="34"/>
+      <c r="CG18" s="33"/>
+      <c r="CH18" s="33"/>
+      <c r="CI18" s="33"/>
+      <c r="CJ18" s="33"/>
+      <c r="CK18" s="33"/>
+      <c r="CL18" s="33"/>
+      <c r="CM18" s="33"/>
+      <c r="CN18" s="35"/>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -4647,7 +5010,7 @@
       <c r="BA19" s="33"/>
       <c r="BB19" s="33"/>
       <c r="BC19" s="33"/>
-      <c r="BD19" s="34"/>
+      <c r="BD19" s="33"/>
       <c r="BE19" s="33"/>
       <c r="BF19" s="33"/>
       <c r="BG19" s="33"/>
@@ -4655,17 +5018,37 @@
       <c r="BI19" s="33"/>
       <c r="BJ19" s="33"/>
       <c r="BK19" s="33"/>
-      <c r="BL19" s="34"/>
+      <c r="BL19" s="33"/>
       <c r="BM19" s="33"/>
-      <c r="BN19" s="33"/>
+      <c r="BN19" s="34"/>
       <c r="BO19" s="33"/>
       <c r="BP19" s="33"/>
       <c r="BQ19" s="33"/>
       <c r="BR19" s="33"/>
       <c r="BS19" s="33"/>
-      <c r="BT19" s="35"/>
+      <c r="BT19" s="33"/>
+      <c r="BU19" s="33"/>
+      <c r="BV19" s="33"/>
+      <c r="BW19" s="33"/>
+      <c r="BX19" s="33"/>
+      <c r="BY19" s="33"/>
+      <c r="BZ19" s="33"/>
+      <c r="CA19" s="33"/>
+      <c r="CB19" s="33"/>
+      <c r="CC19" s="33"/>
+      <c r="CD19" s="33"/>
+      <c r="CE19" s="33"/>
+      <c r="CF19" s="34"/>
+      <c r="CG19" s="33"/>
+      <c r="CH19" s="33"/>
+      <c r="CI19" s="33"/>
+      <c r="CJ19" s="33"/>
+      <c r="CK19" s="33"/>
+      <c r="CL19" s="33"/>
+      <c r="CM19" s="33"/>
+      <c r="CN19" s="35"/>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -4721,7 +5104,7 @@
       <c r="BA20" s="33"/>
       <c r="BB20" s="33"/>
       <c r="BC20" s="33"/>
-      <c r="BD20" s="34"/>
+      <c r="BD20" s="33"/>
       <c r="BE20" s="33"/>
       <c r="BF20" s="33"/>
       <c r="BG20" s="33"/>
@@ -4729,17 +5112,37 @@
       <c r="BI20" s="33"/>
       <c r="BJ20" s="33"/>
       <c r="BK20" s="33"/>
-      <c r="BL20" s="34"/>
+      <c r="BL20" s="33"/>
       <c r="BM20" s="33"/>
-      <c r="BN20" s="33"/>
+      <c r="BN20" s="34"/>
       <c r="BO20" s="33"/>
       <c r="BP20" s="33"/>
       <c r="BQ20" s="33"/>
       <c r="BR20" s="33"/>
       <c r="BS20" s="33"/>
-      <c r="BT20" s="35"/>
+      <c r="BT20" s="33"/>
+      <c r="BU20" s="33"/>
+      <c r="BV20" s="33"/>
+      <c r="BW20" s="33"/>
+      <c r="BX20" s="33"/>
+      <c r="BY20" s="33"/>
+      <c r="BZ20" s="33"/>
+      <c r="CA20" s="33"/>
+      <c r="CB20" s="33"/>
+      <c r="CC20" s="33"/>
+      <c r="CD20" s="33"/>
+      <c r="CE20" s="33"/>
+      <c r="CF20" s="34"/>
+      <c r="CG20" s="33"/>
+      <c r="CH20" s="33"/>
+      <c r="CI20" s="33"/>
+      <c r="CJ20" s="33"/>
+      <c r="CK20" s="33"/>
+      <c r="CL20" s="33"/>
+      <c r="CM20" s="33"/>
+      <c r="CN20" s="35"/>
     </row>
-    <row r="21" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A21" s="20"/>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -4795,7 +5198,7 @@
       <c r="BA21" s="33"/>
       <c r="BB21" s="33"/>
       <c r="BC21" s="33"/>
-      <c r="BD21" s="35"/>
+      <c r="BD21" s="33"/>
       <c r="BE21" s="33"/>
       <c r="BF21" s="33"/>
       <c r="BG21" s="33"/>
@@ -4803,17 +5206,37 @@
       <c r="BI21" s="33"/>
       <c r="BJ21" s="33"/>
       <c r="BK21" s="33"/>
-      <c r="BL21" s="35"/>
+      <c r="BL21" s="33"/>
       <c r="BM21" s="33"/>
-      <c r="BN21" s="33"/>
+      <c r="BN21" s="35"/>
       <c r="BO21" s="33"/>
       <c r="BP21" s="33"/>
       <c r="BQ21" s="33"/>
       <c r="BR21" s="33"/>
       <c r="BS21" s="33"/>
-      <c r="BT21" s="35"/>
+      <c r="BT21" s="33"/>
+      <c r="BU21" s="33"/>
+      <c r="BV21" s="33"/>
+      <c r="BW21" s="33"/>
+      <c r="BX21" s="33"/>
+      <c r="BY21" s="33"/>
+      <c r="BZ21" s="33"/>
+      <c r="CA21" s="33"/>
+      <c r="CB21" s="33"/>
+      <c r="CC21" s="33"/>
+      <c r="CD21" s="33"/>
+      <c r="CE21" s="33"/>
+      <c r="CF21" s="35"/>
+      <c r="CG21" s="33"/>
+      <c r="CH21" s="33"/>
+      <c r="CI21" s="33"/>
+      <c r="CJ21" s="33"/>
+      <c r="CK21" s="33"/>
+      <c r="CL21" s="33"/>
+      <c r="CM21" s="33"/>
+      <c r="CN21" s="35"/>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A22" s="20"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -4869,7 +5292,7 @@
       <c r="BA22" s="33"/>
       <c r="BB22" s="33"/>
       <c r="BC22" s="33"/>
-      <c r="BD22" s="35"/>
+      <c r="BD22" s="33"/>
       <c r="BE22" s="33"/>
       <c r="BF22" s="33"/>
       <c r="BG22" s="33"/>
@@ -4877,17 +5300,37 @@
       <c r="BI22" s="33"/>
       <c r="BJ22" s="33"/>
       <c r="BK22" s="33"/>
-      <c r="BL22" s="35"/>
+      <c r="BL22" s="33"/>
       <c r="BM22" s="33"/>
-      <c r="BN22" s="33"/>
+      <c r="BN22" s="35"/>
       <c r="BO22" s="33"/>
       <c r="BP22" s="33"/>
       <c r="BQ22" s="33"/>
       <c r="BR22" s="33"/>
       <c r="BS22" s="33"/>
-      <c r="BT22" s="35"/>
+      <c r="BT22" s="33"/>
+      <c r="BU22" s="33"/>
+      <c r="BV22" s="33"/>
+      <c r="BW22" s="33"/>
+      <c r="BX22" s="33"/>
+      <c r="BY22" s="33"/>
+      <c r="BZ22" s="33"/>
+      <c r="CA22" s="33"/>
+      <c r="CB22" s="33"/>
+      <c r="CC22" s="33"/>
+      <c r="CD22" s="33"/>
+      <c r="CE22" s="33"/>
+      <c r="CF22" s="35"/>
+      <c r="CG22" s="33"/>
+      <c r="CH22" s="33"/>
+      <c r="CI22" s="33"/>
+      <c r="CJ22" s="33"/>
+      <c r="CK22" s="33"/>
+      <c r="CL22" s="33"/>
+      <c r="CM22" s="33"/>
+      <c r="CN22" s="35"/>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A23" s="20"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -4943,7 +5386,7 @@
       <c r="BA23" s="33"/>
       <c r="BB23" s="33"/>
       <c r="BC23" s="33"/>
-      <c r="BD23" s="35"/>
+      <c r="BD23" s="33"/>
       <c r="BE23" s="33"/>
       <c r="BF23" s="33"/>
       <c r="BG23" s="33"/>
@@ -4951,17 +5394,37 @@
       <c r="BI23" s="33"/>
       <c r="BJ23" s="33"/>
       <c r="BK23" s="33"/>
-      <c r="BL23" s="35"/>
+      <c r="BL23" s="33"/>
       <c r="BM23" s="33"/>
-      <c r="BN23" s="33"/>
+      <c r="BN23" s="35"/>
       <c r="BO23" s="33"/>
       <c r="BP23" s="33"/>
       <c r="BQ23" s="33"/>
       <c r="BR23" s="33"/>
       <c r="BS23" s="33"/>
-      <c r="BT23" s="35"/>
+      <c r="BT23" s="33"/>
+      <c r="BU23" s="33"/>
+      <c r="BV23" s="33"/>
+      <c r="BW23" s="33"/>
+      <c r="BX23" s="33"/>
+      <c r="BY23" s="33"/>
+      <c r="BZ23" s="33"/>
+      <c r="CA23" s="33"/>
+      <c r="CB23" s="33"/>
+      <c r="CC23" s="33"/>
+      <c r="CD23" s="33"/>
+      <c r="CE23" s="33"/>
+      <c r="CF23" s="35"/>
+      <c r="CG23" s="33"/>
+      <c r="CH23" s="33"/>
+      <c r="CI23" s="33"/>
+      <c r="CJ23" s="33"/>
+      <c r="CK23" s="33"/>
+      <c r="CL23" s="33"/>
+      <c r="CM23" s="33"/>
+      <c r="CN23" s="35"/>
     </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A24" s="20"/>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -5017,7 +5480,7 @@
       <c r="BA24" s="33"/>
       <c r="BB24" s="33"/>
       <c r="BC24" s="33"/>
-      <c r="BD24" s="35"/>
+      <c r="BD24" s="33"/>
       <c r="BE24" s="33"/>
       <c r="BF24" s="33"/>
       <c r="BG24" s="33"/>
@@ -5025,17 +5488,37 @@
       <c r="BI24" s="33"/>
       <c r="BJ24" s="33"/>
       <c r="BK24" s="33"/>
-      <c r="BL24" s="35"/>
+      <c r="BL24" s="33"/>
       <c r="BM24" s="33"/>
-      <c r="BN24" s="33"/>
+      <c r="BN24" s="35"/>
       <c r="BO24" s="33"/>
       <c r="BP24" s="33"/>
       <c r="BQ24" s="33"/>
       <c r="BR24" s="33"/>
       <c r="BS24" s="33"/>
-      <c r="BT24" s="35"/>
+      <c r="BT24" s="33"/>
+      <c r="BU24" s="33"/>
+      <c r="BV24" s="33"/>
+      <c r="BW24" s="33"/>
+      <c r="BX24" s="33"/>
+      <c r="BY24" s="33"/>
+      <c r="BZ24" s="33"/>
+      <c r="CA24" s="33"/>
+      <c r="CB24" s="33"/>
+      <c r="CC24" s="33"/>
+      <c r="CD24" s="33"/>
+      <c r="CE24" s="33"/>
+      <c r="CF24" s="35"/>
+      <c r="CG24" s="33"/>
+      <c r="CH24" s="33"/>
+      <c r="CI24" s="33"/>
+      <c r="CJ24" s="33"/>
+      <c r="CK24" s="33"/>
+      <c r="CL24" s="33"/>
+      <c r="CM24" s="33"/>
+      <c r="CN24" s="35"/>
     </row>
-    <row r="25" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -5091,7 +5574,7 @@
       <c r="BA25" s="33"/>
       <c r="BB25" s="33"/>
       <c r="BC25" s="33"/>
-      <c r="BD25" s="35"/>
+      <c r="BD25" s="33"/>
       <c r="BE25" s="33"/>
       <c r="BF25" s="33"/>
       <c r="BG25" s="33"/>
@@ -5099,17 +5582,37 @@
       <c r="BI25" s="33"/>
       <c r="BJ25" s="33"/>
       <c r="BK25" s="33"/>
-      <c r="BL25" s="35"/>
+      <c r="BL25" s="33"/>
       <c r="BM25" s="33"/>
-      <c r="BN25" s="33"/>
+      <c r="BN25" s="35"/>
       <c r="BO25" s="33"/>
       <c r="BP25" s="33"/>
       <c r="BQ25" s="33"/>
       <c r="BR25" s="33"/>
       <c r="BS25" s="33"/>
-      <c r="BT25" s="35"/>
+      <c r="BT25" s="33"/>
+      <c r="BU25" s="33"/>
+      <c r="BV25" s="33"/>
+      <c r="BW25" s="33"/>
+      <c r="BX25" s="33"/>
+      <c r="BY25" s="33"/>
+      <c r="BZ25" s="33"/>
+      <c r="CA25" s="33"/>
+      <c r="CB25" s="33"/>
+      <c r="CC25" s="33"/>
+      <c r="CD25" s="33"/>
+      <c r="CE25" s="33"/>
+      <c r="CF25" s="35"/>
+      <c r="CG25" s="33"/>
+      <c r="CH25" s="33"/>
+      <c r="CI25" s="33"/>
+      <c r="CJ25" s="33"/>
+      <c r="CK25" s="33"/>
+      <c r="CL25" s="33"/>
+      <c r="CM25" s="33"/>
+      <c r="CN25" s="35"/>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -5165,7 +5668,7 @@
       <c r="BA26" s="33"/>
       <c r="BB26" s="33"/>
       <c r="BC26" s="33"/>
-      <c r="BD26" s="35"/>
+      <c r="BD26" s="33"/>
       <c r="BE26" s="33"/>
       <c r="BF26" s="33"/>
       <c r="BG26" s="33"/>
@@ -5173,17 +5676,37 @@
       <c r="BI26" s="33"/>
       <c r="BJ26" s="33"/>
       <c r="BK26" s="33"/>
-      <c r="BL26" s="35"/>
+      <c r="BL26" s="33"/>
       <c r="BM26" s="33"/>
-      <c r="BN26" s="33"/>
+      <c r="BN26" s="35"/>
       <c r="BO26" s="33"/>
       <c r="BP26" s="33"/>
       <c r="BQ26" s="33"/>
       <c r="BR26" s="33"/>
       <c r="BS26" s="33"/>
-      <c r="BT26" s="35"/>
+      <c r="BT26" s="33"/>
+      <c r="BU26" s="33"/>
+      <c r="BV26" s="33"/>
+      <c r="BW26" s="33"/>
+      <c r="BX26" s="33"/>
+      <c r="BY26" s="33"/>
+      <c r="BZ26" s="33"/>
+      <c r="CA26" s="33"/>
+      <c r="CB26" s="33"/>
+      <c r="CC26" s="33"/>
+      <c r="CD26" s="33"/>
+      <c r="CE26" s="33"/>
+      <c r="CF26" s="35"/>
+      <c r="CG26" s="33"/>
+      <c r="CH26" s="33"/>
+      <c r="CI26" s="33"/>
+      <c r="CJ26" s="33"/>
+      <c r="CK26" s="33"/>
+      <c r="CL26" s="33"/>
+      <c r="CM26" s="33"/>
+      <c r="CN26" s="35"/>
     </row>
-    <row r="27" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:92" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -5239,37 +5762,57 @@
       <c r="BA27" s="60"/>
       <c r="BB27" s="60"/>
       <c r="BC27" s="60"/>
-      <c r="BD27" s="61"/>
-      <c r="BE27" s="59"/>
+      <c r="BD27" s="60"/>
+      <c r="BE27" s="60"/>
       <c r="BF27" s="60"/>
       <c r="BG27" s="60"/>
       <c r="BH27" s="60"/>
       <c r="BI27" s="60"/>
       <c r="BJ27" s="60"/>
       <c r="BK27" s="60"/>
-      <c r="BL27" s="61"/>
-      <c r="BM27" s="59"/>
-      <c r="BN27" s="60"/>
-      <c r="BO27" s="60"/>
+      <c r="BL27" s="60"/>
+      <c r="BM27" s="60"/>
+      <c r="BN27" s="61"/>
+      <c r="BO27" s="59"/>
       <c r="BP27" s="60"/>
       <c r="BQ27" s="60"/>
       <c r="BR27" s="60"/>
       <c r="BS27" s="60"/>
-      <c r="BT27" s="61"/>
+      <c r="BT27" s="60"/>
+      <c r="BU27" s="60"/>
+      <c r="BV27" s="60"/>
+      <c r="BW27" s="60"/>
+      <c r="BX27" s="60"/>
+      <c r="BY27" s="60"/>
+      <c r="BZ27" s="60"/>
+      <c r="CA27" s="60"/>
+      <c r="CB27" s="60"/>
+      <c r="CC27" s="60"/>
+      <c r="CD27" s="60"/>
+      <c r="CE27" s="60"/>
+      <c r="CF27" s="61"/>
+      <c r="CG27" s="59"/>
+      <c r="CH27" s="60"/>
+      <c r="CI27" s="60"/>
+      <c r="CJ27" s="60"/>
+      <c r="CK27" s="60"/>
+      <c r="CL27" s="60"/>
+      <c r="CM27" s="60"/>
+      <c r="CN27" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="BM6:BT6"/>
+    <mergeCell ref="CG6:CN6"/>
     <mergeCell ref="A2:Q3"/>
     <mergeCell ref="A5:AV5"/>
-    <mergeCell ref="AW5:BT5"/>
+    <mergeCell ref="AW5:CN5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="AW6:BD6"/>
-    <mergeCell ref="BE6:BL6"/>
+    <mergeCell ref="AW6:BN6"/>
+    <mergeCell ref="BO6:CF6"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="B6:B7"/>
   </mergeCells>
